--- a/Employee_Reports_wi48/Renz Jake Orense Lontoc Q0468.xlsx
+++ b/Employee_Reports_wi48/Renz Jake Orense Lontoc Q0468.xlsx
@@ -554,11 +554,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-349</v>
+        <v>-352</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
